--- a/output_tables/p_ggps_pts1_groupno.xlsx
+++ b/output_tables/p_ggps_pts1_groupno.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/output_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{31F521CB-BA45-4674-92A1-DCF50DD73465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{236CF9A6-0AD5-4B98-A8A7-D840C5F8CE3C}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{31F521CB-BA45-4674-92A1-DCF50DD73465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2179F81-B1D0-4560-AFCE-3DC13194D2BA}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="60" windowWidth="28635" windowHeight="15390" xr2:uid="{40AFBA6D-CE40-4C81-9389-4C5F39FB87B5}"/>
+    <workbookView xWindow="-60" yWindow="15" windowWidth="28635" windowHeight="15390" xr2:uid="{40AFBA6D-CE40-4C81-9389-4C5F39FB87B5}"/>
   </bookViews>
   <sheets>
     <sheet name="p_ggps_pts1_groupno" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5349" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5512" uniqueCount="719">
   <si>
     <t>site_location</t>
   </si>
@@ -2144,13 +2157,49 @@
   </si>
   <si>
     <t>4, 0.0625 m2 rebar quads planted (chia pets)</t>
+  </si>
+  <si>
+    <t>group_no_count</t>
+  </si>
+  <si>
+    <t>group multi-cases</t>
+  </si>
+  <si>
+    <t>plt_loc_code count</t>
+  </si>
+  <si>
+    <t>loc multi-cases</t>
+  </si>
+  <si>
+    <t>geometry</t>
+  </si>
+  <si>
+    <t>addint donor site to key would differentiate</t>
+  </si>
+  <si>
+    <t>different dates in 2021</t>
+  </si>
+  <si>
+    <t>different methods</t>
+  </si>
+  <si>
+    <t>but slightly different coords</t>
+  </si>
+  <si>
+    <t>no coords</t>
+  </si>
+  <si>
+    <t>replicates</t>
+  </si>
+  <si>
+    <t>repeat / colated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2285,8 +2334,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2472,8 +2528,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2603,6 +2677,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2648,13 +2733,22 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2711,6 +2805,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3030,8 +3128,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B25B4A92-AD6D-4C8D-856E-82DBE97ED9B3}">
-  <dimension ref="A1:AF289"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AL289"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" hidden="1" customWidth="1"/>
@@ -3065,9 +3163,14 @@
     <col min="30" max="30" width="255.7109375" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="36" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16.7109375" customWidth="1"/>
+    <col min="34" max="35" width="17.85546875" customWidth="1"/>
+    <col min="36" max="36" width="19.28515625" customWidth="1"/>
+    <col min="37" max="37" width="23.5703125" customWidth="1"/>
+    <col min="38" max="38" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -3161,8 +3264,20 @@
       <c r="AF1" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="AG1" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>710</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3259,8 +3374,24 @@
       <c r="AF2">
         <v>1</v>
       </c>
+      <c r="AG2">
+        <f>COUNTIF(AF:AF,AF2)</f>
+        <v>1</v>
+      </c>
+      <c r="AH2" s="6" t="str">
+        <f>IF(AG2&gt;1,AF2,"")</f>
+        <v/>
+      </c>
+      <c r="AI2">
+        <f>COUNTIF(D:D,D2)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="str">
+        <f>IF(AI2&gt;1,D2,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3357,8 +3488,24 @@
       <c r="AF3">
         <v>2</v>
       </c>
+      <c r="AG3">
+        <f t="shared" ref="AG3:AG66" si="0">COUNTIF(AF:AF,AF3)</f>
+        <v>1</v>
+      </c>
+      <c r="AH3" s="6" t="str">
+        <f t="shared" ref="AH3:AH66" si="1">IF(AG3&gt;1,AF3,"")</f>
+        <v/>
+      </c>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI66" si="2">COUNTIF(D:D,D3)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="str">
+        <f t="shared" ref="AJ3:AJ66" si="3">IF(AI3&gt;1,D3,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3455,8 +3602,24 @@
       <c r="AF4">
         <v>3</v>
       </c>
+      <c r="AG4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH4" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3553,8 +3716,24 @@
       <c r="AF5">
         <v>4</v>
       </c>
+      <c r="AG5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH5" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3651,8 +3830,24 @@
       <c r="AF6">
         <v>5</v>
       </c>
+      <c r="AG6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH6" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3749,8 +3944,27 @@
       <c r="AF7">
         <v>6</v>
       </c>
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH7" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_west_L1</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3847,8 +4061,27 @@
       <c r="AF8">
         <v>6</v>
       </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH8" s="6">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_west_L1</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3945,8 +4178,27 @@
       <c r="AF9">
         <v>7</v>
       </c>
+      <c r="AG9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH9" s="6">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L1</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4043,8 +4295,27 @@
       <c r="AF10">
         <v>7</v>
       </c>
+      <c r="AG10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH10" s="6">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L1</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4141,8 +4412,27 @@
       <c r="AF11">
         <v>8</v>
       </c>
+      <c r="AG11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH11" s="6">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L2</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4239,8 +4529,27 @@
       <c r="AF12">
         <v>8</v>
       </c>
+      <c r="AG12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH12" s="6">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L2</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4337,8 +4646,27 @@
       <c r="AF13">
         <v>9</v>
       </c>
+      <c r="AG13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH13" s="6">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ13" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L3</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4435,8 +4763,27 @@
       <c r="AF14">
         <v>9</v>
       </c>
+      <c r="AG14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH14" s="6">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L3</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4533,8 +4880,27 @@
       <c r="AF15">
         <v>10</v>
       </c>
+      <c r="AG15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH15" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ15" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L4</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4631,8 +4997,27 @@
       <c r="AF16">
         <v>10</v>
       </c>
+      <c r="AG16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH16" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ16" t="str">
+        <f t="shared" si="3"/>
+        <v>AND_south_L4</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4729,8 +5114,24 @@
       <c r="AF17">
         <v>11</v>
       </c>
+      <c r="AG17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH17" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4827,8 +5228,24 @@
       <c r="AF18">
         <v>12</v>
       </c>
+      <c r="AG18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH18" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI18">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4925,8 +5342,24 @@
       <c r="AF19">
         <v>13</v>
       </c>
+      <c r="AG19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH19" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5023,8 +5456,24 @@
       <c r="AF20">
         <v>14</v>
       </c>
+      <c r="AG20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH20" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5121,8 +5570,24 @@
       <c r="AF21">
         <v>15</v>
       </c>
+      <c r="AG21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH21" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5219,8 +5684,24 @@
       <c r="AF22">
         <v>16</v>
       </c>
+      <c r="AG22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH22" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5317,8 +5798,24 @@
       <c r="AF23">
         <v>17</v>
       </c>
+      <c r="AG23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH23" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI23">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5415,8 +5912,30 @@
       <c r="AF24">
         <v>18</v>
       </c>
+      <c r="AG24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH24" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI24">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>BB_test_1</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>712</v>
+      </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5513,8 +6032,27 @@
       <c r="AF25">
         <v>19</v>
       </c>
+      <c r="AG25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH25" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ25" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>BB_test_1</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5611,8 +6149,27 @@
       <c r="AF26">
         <v>20</v>
       </c>
+      <c r="AG26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH26" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>BB_test_1</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5709,8 +6266,27 @@
       <c r="AF27">
         <v>21</v>
       </c>
+      <c r="AG27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH27" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI27">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>BB_test_1</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5807,8 +6383,27 @@
       <c r="AF28">
         <v>22</v>
       </c>
+      <c r="AG28">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH28" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI28">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="AJ28" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>BB_test_1</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5905,8 +6500,24 @@
       <c r="AF29">
         <v>23</v>
       </c>
+      <c r="AG29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH29" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6003,8 +6614,24 @@
       <c r="AF30">
         <v>24</v>
       </c>
+      <c r="AG30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH30" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6101,8 +6728,24 @@
       <c r="AF31">
         <v>25</v>
       </c>
+      <c r="AG31">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH31" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6199,8 +6842,27 @@
       <c r="AF32">
         <v>26</v>
       </c>
+      <c r="AG32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH32" s="6">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="AI32">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ32" t="str">
+        <f t="shared" si="3"/>
+        <v>COM_L1</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6297,8 +6959,27 @@
       <c r="AF33">
         <v>26</v>
       </c>
+      <c r="AG33">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH33" s="6">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="AI33">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ33" t="str">
+        <f t="shared" si="3"/>
+        <v>COM_L1</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6395,8 +7076,27 @@
       <c r="AF34">
         <v>27</v>
       </c>
+      <c r="AG34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH34" s="6">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AI34">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ34" t="str">
+        <f t="shared" si="3"/>
+        <v>COM_L2</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6493,8 +7193,27 @@
       <c r="AF35">
         <v>27</v>
       </c>
+      <c r="AG35">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH35" s="6">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="AI35">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ35" t="str">
+        <f t="shared" si="3"/>
+        <v>COM_L2</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6591,8 +7310,27 @@
       <c r="AF36">
         <v>28</v>
       </c>
+      <c r="AG36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH36" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI36">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ36" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_1</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6689,8 +7427,27 @@
       <c r="AF37">
         <v>29</v>
       </c>
+      <c r="AG37">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH37" s="6">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AI37">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ37" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_L1</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6787,8 +7544,27 @@
       <c r="AF38">
         <v>29</v>
       </c>
+      <c r="AG38">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH38" s="6">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="AI38">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ38" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_L1</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6885,8 +7661,27 @@
       <c r="AF39">
         <v>30</v>
       </c>
+      <c r="AG39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH39" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI39">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ39" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_P1</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6983,8 +7778,27 @@
       <c r="AF40">
         <v>30</v>
       </c>
+      <c r="AG40">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH40" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI40">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ40" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_P1</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7081,8 +7895,27 @@
       <c r="AF41">
         <v>30</v>
       </c>
+      <c r="AG41">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH41" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI41">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ41" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_P1</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7179,8 +8012,27 @@
       <c r="AF42">
         <v>30</v>
       </c>
+      <c r="AG42">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH42" s="6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AI42">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ42" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_P1</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7277,8 +8129,27 @@
       <c r="AF43">
         <v>31</v>
       </c>
+      <c r="AG43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH43" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI43">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ43" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_3</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7375,8 +8246,24 @@
       <c r="AF44">
         <v>32</v>
       </c>
+      <c r="AG44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH44" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI44">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7473,8 +8360,27 @@
       <c r="AF45">
         <v>33</v>
       </c>
+      <c r="AG45">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH45" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI45">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ45" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_1</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7571,8 +8477,27 @@
       <c r="AF46">
         <v>34</v>
       </c>
+      <c r="AG46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH46" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI46">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AJ46" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DEL_3</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7669,8 +8594,24 @@
       <c r="AF47">
         <v>35</v>
       </c>
+      <c r="AG47">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH47" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI47">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7767,8 +8708,24 @@
       <c r="AF48">
         <v>36</v>
       </c>
+      <c r="AG48">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH48" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI48">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ48" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7865,8 +8822,24 @@
       <c r="AF49">
         <v>37</v>
       </c>
+      <c r="AG49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH49" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI49">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7963,8 +8936,24 @@
       <c r="AF50">
         <v>38</v>
       </c>
+      <c r="AG50">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH50" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI50">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ50" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8061,8 +9050,24 @@
       <c r="AF51">
         <v>39</v>
       </c>
+      <c r="AG51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH51" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI51">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ51" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8159,8 +9164,24 @@
       <c r="AF52">
         <v>40</v>
       </c>
+      <c r="AG52">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH52" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI52">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ52" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8257,8 +9278,30 @@
       <c r="AF53">
         <v>41</v>
       </c>
+      <c r="AG53">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH53" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI53">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ53" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DB_test_2</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>713</v>
+      </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8355,8 +9398,27 @@
       <c r="AF54">
         <v>42</v>
       </c>
+      <c r="AG54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH54" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI54">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ54" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DB_test_2</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8453,8 +9515,27 @@
       <c r="AF55">
         <v>43</v>
       </c>
+      <c r="AG55">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH55" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI55">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ55" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DB_test_2</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8551,8 +9632,27 @@
       <c r="AF56">
         <v>44</v>
       </c>
+      <c r="AG56">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH56" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI56">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ56" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>DB_test_2</v>
+      </c>
+      <c r="AK56" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8649,8 +9749,24 @@
       <c r="AF57">
         <v>45</v>
       </c>
+      <c r="AG57">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH57" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI57">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8747,8 +9863,24 @@
       <c r="AF58">
         <v>46</v>
       </c>
+      <c r="AG58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI58">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ58" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8845,8 +9977,24 @@
       <c r="AF59">
         <v>47</v>
       </c>
+      <c r="AG59">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH59" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI59">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8943,8 +10091,24 @@
       <c r="AF60">
         <v>48</v>
       </c>
+      <c r="AG60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH60" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI60">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ60" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9041,8 +10205,24 @@
       <c r="AF61">
         <v>49</v>
       </c>
+      <c r="AG61">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH61" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI61">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ61" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9139,8 +10319,24 @@
       <c r="AF62">
         <v>50</v>
       </c>
+      <c r="AG62">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH62" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI62">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ62" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9237,8 +10433,24 @@
       <c r="AF63">
         <v>51</v>
       </c>
+      <c r="AG63">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH63" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI63">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ63" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9335,8 +10547,24 @@
       <c r="AF64">
         <v>52</v>
       </c>
+      <c r="AG64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH64" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AI64">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9433,8 +10661,27 @@
       <c r="AF65">
         <v>53</v>
       </c>
+      <c r="AG65">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH65" s="6">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="AI65">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ65" t="str">
+        <f t="shared" si="3"/>
+        <v>FDG_L1</v>
+      </c>
+      <c r="AK65" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9531,8 +10778,27 @@
       <c r="AF66">
         <v>53</v>
       </c>
+      <c r="AG66">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH66" s="6">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="AI66">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AJ66" t="str">
+        <f t="shared" si="3"/>
+        <v>FDG_L1</v>
+      </c>
+      <c r="AK66" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9629,8 +10895,27 @@
       <c r="AF67">
         <v>54</v>
       </c>
+      <c r="AG67">
+        <f t="shared" ref="AG67:AG130" si="4">COUNTIF(AF:AF,AF67)</f>
+        <v>2</v>
+      </c>
+      <c r="AH67" s="6">
+        <f t="shared" ref="AH67:AH130" si="5">IF(AG67&gt;1,AF67,"")</f>
+        <v>54</v>
+      </c>
+      <c r="AI67">
+        <f t="shared" ref="AI67:AI130" si="6">COUNTIF(D:D,D67)</f>
+        <v>4</v>
+      </c>
+      <c r="AJ67" t="str">
+        <f t="shared" ref="AJ67:AJ130" si="7">IF(AI67&gt;1,D67,"")</f>
+        <v>FDG_L2</v>
+      </c>
+      <c r="AK67" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9727,8 +11012,27 @@
       <c r="AF68">
         <v>54</v>
       </c>
+      <c r="AG68">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH68" s="6">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="AI68">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ68" t="str">
+        <f t="shared" si="7"/>
+        <v>FDG_L2</v>
+      </c>
+      <c r="AK68" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9825,8 +11129,27 @@
       <c r="AF69">
         <v>55</v>
       </c>
+      <c r="AG69">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH69" s="6">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="AI69">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ69" t="str">
+        <f t="shared" si="7"/>
+        <v>FDG_L1</v>
+      </c>
+      <c r="AK69" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9923,8 +11246,27 @@
       <c r="AF70">
         <v>55</v>
       </c>
+      <c r="AG70">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH70" s="6">
+        <f t="shared" si="5"/>
+        <v>55</v>
+      </c>
+      <c r="AI70">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ70" t="str">
+        <f t="shared" si="7"/>
+        <v>FDG_L1</v>
+      </c>
+      <c r="AK70" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -10021,8 +11363,27 @@
       <c r="AF71">
         <v>56</v>
       </c>
+      <c r="AG71">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH71" s="6">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+      <c r="AI71">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ71" t="str">
+        <f t="shared" si="7"/>
+        <v>FDG_L2</v>
+      </c>
+      <c r="AK71" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -10119,8 +11480,27 @@
       <c r="AF72">
         <v>56</v>
       </c>
+      <c r="AG72">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH72" s="6">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+      <c r="AI72">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ72" t="str">
+        <f t="shared" si="7"/>
+        <v>FDG_L2</v>
+      </c>
+      <c r="AK72" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -10217,8 +11597,24 @@
       <c r="AF73">
         <v>57</v>
       </c>
+      <c r="AG73">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH73" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI73">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10315,8 +11711,24 @@
       <c r="AF74">
         <v>58</v>
       </c>
+      <c r="AG74">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH74" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI74">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10413,8 +11825,24 @@
       <c r="AF75">
         <v>59</v>
       </c>
+      <c r="AG75">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH75" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI75">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10511,8 +11939,24 @@
       <c r="AF76">
         <v>60</v>
       </c>
+      <c r="AG76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH76" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI76">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ76" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10609,8 +12053,30 @@
       <c r="AF77">
         <v>61</v>
       </c>
+      <c r="AG77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH77" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI77">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ77" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_4</v>
+      </c>
+      <c r="AK77" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>714</v>
+      </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10707,8 +12173,27 @@
       <c r="AF78">
         <v>62</v>
       </c>
+      <c r="AG78">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH78" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI78">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ78" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_4</v>
+      </c>
+      <c r="AK78" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10805,8 +12290,24 @@
       <c r="AF79">
         <v>63</v>
       </c>
+      <c r="AG79">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH79" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI79">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ79" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10903,8 +12404,27 @@
       <c r="AF80">
         <v>64</v>
       </c>
+      <c r="AG80">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH80" s="6">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
+      <c r="AI80">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ80" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_deep_L1</v>
+      </c>
+      <c r="AK80" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -11001,8 +12521,27 @@
       <c r="AF81">
         <v>64</v>
       </c>
+      <c r="AG81">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH81" s="6">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
+      <c r="AI81">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ81" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_deep_L1</v>
+      </c>
+      <c r="AK81" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -11099,8 +12638,27 @@
       <c r="AF82">
         <v>65</v>
       </c>
+      <c r="AG82">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH82" s="6">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+      <c r="AI82">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ82" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_shallow_L1</v>
+      </c>
+      <c r="AK82" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -11197,8 +12755,27 @@
       <c r="AF83">
         <v>65</v>
       </c>
+      <c r="AG83">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH83" s="6">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+      <c r="AI83">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ83" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_shallow_L1</v>
+      </c>
+      <c r="AK83" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -11295,8 +12872,27 @@
       <c r="AF84">
         <v>66</v>
       </c>
+      <c r="AG84">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH84" s="6">
+        <f t="shared" si="5"/>
+        <v>66</v>
+      </c>
+      <c r="AI84">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ84" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_shallow_L2</v>
+      </c>
+      <c r="AK84" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11393,8 +12989,27 @@
       <c r="AF85">
         <v>66</v>
       </c>
+      <c r="AG85">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH85" s="6">
+        <f t="shared" si="5"/>
+        <v>66</v>
+      </c>
+      <c r="AI85">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ85" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_shallow_L2</v>
+      </c>
+      <c r="AK85" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11491,8 +13106,27 @@
       <c r="AF86">
         <v>67</v>
       </c>
+      <c r="AG86">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH86" s="6">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="AI86">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ86" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_shallow_L3</v>
+      </c>
+      <c r="AK86" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11589,8 +13223,27 @@
       <c r="AF87">
         <v>67</v>
       </c>
+      <c r="AG87">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH87" s="6">
+        <f t="shared" si="5"/>
+        <v>67</v>
+      </c>
+      <c r="AI87">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ87" t="str">
+        <f t="shared" si="7"/>
+        <v>HAR_shallow_L3</v>
+      </c>
+      <c r="AK87" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11687,8 +13340,24 @@
       <c r="AF88">
         <v>68</v>
       </c>
+      <c r="AG88">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH88" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI88">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ88" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11785,8 +13454,24 @@
       <c r="AF89">
         <v>69</v>
       </c>
+      <c r="AG89">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH89" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI89">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ89" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -11883,8 +13568,24 @@
       <c r="AF90">
         <v>70</v>
       </c>
+      <c r="AG90">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH90" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI90">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ90" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -11981,8 +13682,24 @@
       <c r="AF91">
         <v>71</v>
       </c>
+      <c r="AG91">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH91" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI91">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ91" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12079,8 +13796,27 @@
       <c r="AF92">
         <v>72</v>
       </c>
+      <c r="AG92">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH92" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI92">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ92" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>HPT_north_2</v>
+      </c>
+      <c r="AK92" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12177,8 +13913,24 @@
       <c r="AF93">
         <v>73</v>
       </c>
+      <c r="AG93">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH93" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI93">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ93" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12275,8 +14027,30 @@
       <c r="AF94">
         <v>74</v>
       </c>
+      <c r="AG94">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH94" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI94">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ94" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>HPT_north_2</v>
+      </c>
+      <c r="AK94" t="s">
+        <v>162</v>
+      </c>
+      <c r="AL94" t="s">
+        <v>715</v>
+      </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12373,8 +14147,24 @@
       <c r="AF95">
         <v>75</v>
       </c>
+      <c r="AG95">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH95" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI95">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ95" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12471,8 +14261,24 @@
       <c r="AF96">
         <v>76</v>
       </c>
+      <c r="AG96">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH96" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI96">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ96" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12569,8 +14375,27 @@
       <c r="AF97">
         <v>77</v>
       </c>
+      <c r="AG97">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH97" s="6">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="AI97">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ97" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_south_P1</v>
+      </c>
+      <c r="AK97" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -12667,8 +14492,27 @@
       <c r="AF98">
         <v>77</v>
       </c>
+      <c r="AG98">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH98" s="6">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="AI98">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ98" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_south_P1</v>
+      </c>
+      <c r="AK98" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12765,8 +14609,27 @@
       <c r="AF99">
         <v>77</v>
       </c>
+      <c r="AG99">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH99" s="6">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="AI99">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ99" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_south_P1</v>
+      </c>
+      <c r="AK99" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -12863,8 +14726,27 @@
       <c r="AF100">
         <v>77</v>
       </c>
+      <c r="AG100">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH100" s="6">
+        <f t="shared" si="5"/>
+        <v>77</v>
+      </c>
+      <c r="AI100">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ100" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_south_P1</v>
+      </c>
+      <c r="AK100" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -12961,8 +14843,27 @@
       <c r="AF101">
         <v>78</v>
       </c>
+      <c r="AG101">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH101" s="6">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="AI101">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ101" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_north_P1</v>
+      </c>
+      <c r="AK101" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -13059,8 +14960,27 @@
       <c r="AF102">
         <v>78</v>
       </c>
+      <c r="AG102">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH102" s="6">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="AI102">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ102" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_north_P1</v>
+      </c>
+      <c r="AK102" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -13157,8 +15077,27 @@
       <c r="AF103">
         <v>78</v>
       </c>
+      <c r="AG103">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH103" s="6">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="AI103">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ103" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_north_P1</v>
+      </c>
+      <c r="AK103" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -13255,8 +15194,27 @@
       <c r="AF104">
         <v>78</v>
       </c>
+      <c r="AG104">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH104" s="6">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="AI104">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ104" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_north_P1</v>
+      </c>
+      <c r="AK104" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -13353,8 +15311,24 @@
       <c r="AF105">
         <v>79</v>
       </c>
+      <c r="AG105">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH105" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI105">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ105" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -13451,8 +15425,27 @@
       <c r="AF106">
         <v>80</v>
       </c>
+      <c r="AG106">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH106" s="6">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="AI106">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ106" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_north</v>
+      </c>
+      <c r="AK106" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -13549,8 +15542,27 @@
       <c r="AF107">
         <v>80</v>
       </c>
+      <c r="AG107">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH107" s="6">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="AI107">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ107" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_north</v>
+      </c>
+      <c r="AK107" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -13647,8 +15659,27 @@
       <c r="AF108">
         <v>81</v>
       </c>
+      <c r="AG108">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH108" s="6">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="AI108">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ108" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P1</v>
+      </c>
+      <c r="AK108" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -13745,8 +15776,27 @@
       <c r="AF109">
         <v>81</v>
       </c>
+      <c r="AG109">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH109" s="6">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="AI109">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ109" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P1</v>
+      </c>
+      <c r="AK109" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -13843,8 +15893,27 @@
       <c r="AF110">
         <v>81</v>
       </c>
+      <c r="AG110">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH110" s="6">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="AI110">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ110" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P1</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -13941,8 +16010,27 @@
       <c r="AF111">
         <v>81</v>
       </c>
+      <c r="AG111">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH111" s="6">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="AI111">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ111" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P1</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -14039,8 +16127,24 @@
       <c r="AF112">
         <v>82</v>
       </c>
+      <c r="AG112">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH112" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AI112">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="AJ112" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -14137,8 +16241,27 @@
       <c r="AF113">
         <v>83</v>
       </c>
+      <c r="AG113">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH113" s="6">
+        <f t="shared" si="5"/>
+        <v>83</v>
+      </c>
+      <c r="AI113">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ113" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_north_L1</v>
+      </c>
+      <c r="AK113" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -14235,8 +16358,27 @@
       <c r="AF114">
         <v>83</v>
       </c>
+      <c r="AG114">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH114" s="6">
+        <f t="shared" si="5"/>
+        <v>83</v>
+      </c>
+      <c r="AI114">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ114" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_north_L1</v>
+      </c>
+      <c r="AK114" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -14333,8 +16475,27 @@
       <c r="AF115">
         <v>84</v>
       </c>
+      <c r="AG115">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH115" s="6">
+        <f t="shared" si="5"/>
+        <v>84</v>
+      </c>
+      <c r="AI115">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ115" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_north_L2</v>
+      </c>
+      <c r="AK115" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -14431,8 +16592,27 @@
       <c r="AF116">
         <v>84</v>
       </c>
+      <c r="AG116">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH116" s="6">
+        <f t="shared" si="5"/>
+        <v>84</v>
+      </c>
+      <c r="AI116">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ116" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_north_L2</v>
+      </c>
+      <c r="AK116" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -14529,8 +16709,27 @@
       <c r="AF117">
         <v>85</v>
       </c>
+      <c r="AG117">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH117" s="6">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="AI117">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ117" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P2</v>
+      </c>
+      <c r="AK117" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -14627,8 +16826,27 @@
       <c r="AF118">
         <v>85</v>
       </c>
+      <c r="AG118">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH118" s="6">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="AI118">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ118" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P2</v>
+      </c>
+      <c r="AK118" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -14725,8 +16943,27 @@
       <c r="AF119">
         <v>85</v>
       </c>
+      <c r="AG119">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH119" s="6">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="AI119">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ119" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P2</v>
+      </c>
+      <c r="AK119" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -14823,8 +17060,27 @@
       <c r="AF120">
         <v>85</v>
       </c>
+      <c r="AG120">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH120" s="6">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
+      <c r="AI120">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ120" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P2</v>
+      </c>
+      <c r="AK120" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -14921,8 +17177,27 @@
       <c r="AF121">
         <v>86</v>
       </c>
+      <c r="AG121">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH121" s="6">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="AI121">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ121" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P3</v>
+      </c>
+      <c r="AK121" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -15019,8 +17294,27 @@
       <c r="AF122">
         <v>86</v>
       </c>
+      <c r="AG122">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH122" s="6">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="AI122">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ122" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P3</v>
+      </c>
+      <c r="AK122" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -15117,8 +17411,27 @@
       <c r="AF123">
         <v>86</v>
       </c>
+      <c r="AG123">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH123" s="6">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="AI123">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ123" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P3</v>
+      </c>
+      <c r="AK123" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -15215,8 +17528,27 @@
       <c r="AF124">
         <v>86</v>
       </c>
+      <c r="AG124">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH124" s="6">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="AI124">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ124" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P3</v>
+      </c>
+      <c r="AK124" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -15313,8 +17645,27 @@
       <c r="AF125">
         <v>87</v>
       </c>
+      <c r="AG125">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH125" s="6">
+        <f t="shared" si="5"/>
+        <v>87</v>
+      </c>
+      <c r="AI125">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ125" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P4</v>
+      </c>
+      <c r="AK125" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -15411,8 +17762,27 @@
       <c r="AF126">
         <v>87</v>
       </c>
+      <c r="AG126">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH126" s="6">
+        <f t="shared" si="5"/>
+        <v>87</v>
+      </c>
+      <c r="AI126">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ126" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P4</v>
+      </c>
+      <c r="AK126" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -15509,8 +17879,27 @@
       <c r="AF127">
         <v>87</v>
       </c>
+      <c r="AG127">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH127" s="6">
+        <f t="shared" si="5"/>
+        <v>87</v>
+      </c>
+      <c r="AI127">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ127" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P4</v>
+      </c>
+      <c r="AK127" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -15607,8 +17996,27 @@
       <c r="AF128">
         <v>87</v>
       </c>
+      <c r="AG128">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH128" s="6">
+        <f t="shared" si="5"/>
+        <v>87</v>
+      </c>
+      <c r="AI128">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AJ128" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_south_P4</v>
+      </c>
+      <c r="AK128" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -15705,8 +18113,27 @@
       <c r="AF129">
         <v>88</v>
       </c>
+      <c r="AG129">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="AH129" s="6">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="AI129">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ129" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_AG1</v>
+      </c>
+      <c r="AK129" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -15803,8 +18230,27 @@
       <c r="AF130">
         <v>88</v>
       </c>
+      <c r="AG130">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="AH130" s="6">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="AI130">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AJ130" t="str">
+        <f t="shared" si="7"/>
+        <v>JSP_mid_BG1</v>
+      </c>
+      <c r="AK130" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -15901,8 +18347,27 @@
       <c r="AF131">
         <v>88</v>
       </c>
+      <c r="AG131">
+        <f t="shared" ref="AG131:AG194" si="8">COUNTIF(AF:AF,AF131)</f>
+        <v>12</v>
+      </c>
+      <c r="AH131" s="6">
+        <f t="shared" ref="AH131:AH194" si="9">IF(AG131&gt;1,AF131,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI131">
+        <f t="shared" ref="AI131:AI194" si="10">COUNTIF(D:D,D131)</f>
+        <v>2</v>
+      </c>
+      <c r="AJ131" t="str">
+        <f t="shared" ref="AJ131:AJ194" si="11">IF(AI131&gt;1,D131,"")</f>
+        <v>JSP_mid_C1</v>
+      </c>
+      <c r="AK131" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -15999,8 +18464,27 @@
       <c r="AF132">
         <v>88</v>
       </c>
+      <c r="AG132">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH132" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI132">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ132" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG2</v>
+      </c>
+      <c r="AK132" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -16097,8 +18581,27 @@
       <c r="AF133">
         <v>88</v>
       </c>
+      <c r="AG133">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH133" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI133">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ133" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C2</v>
+      </c>
+      <c r="AK133" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -16195,8 +18698,27 @@
       <c r="AF134">
         <v>88</v>
       </c>
+      <c r="AG134">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH134" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI134">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ134" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG2</v>
+      </c>
+      <c r="AK134" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -16293,8 +18815,27 @@
       <c r="AF135">
         <v>88</v>
       </c>
+      <c r="AG135">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH135" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI135">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ135" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C3</v>
+      </c>
+      <c r="AK135" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -16391,8 +18932,27 @@
       <c r="AF136">
         <v>88</v>
       </c>
+      <c r="AG136">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH136" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI136">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ136" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG3</v>
+      </c>
+      <c r="AK136" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -16489,8 +19049,27 @@
       <c r="AF137">
         <v>88</v>
       </c>
+      <c r="AG137">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH137" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI137">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ137" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C4</v>
+      </c>
+      <c r="AK137" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -16587,8 +19166,27 @@
       <c r="AF138">
         <v>88</v>
       </c>
+      <c r="AG138">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH138" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI138">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ138" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG4</v>
+      </c>
+      <c r="AK138" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -16685,8 +19283,27 @@
       <c r="AF139">
         <v>88</v>
       </c>
+      <c r="AG139">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH139" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI139">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ139" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG3</v>
+      </c>
+      <c r="AK139" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -16783,8 +19400,27 @@
       <c r="AF140">
         <v>88</v>
       </c>
+      <c r="AG140">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH140" s="6">
+        <f t="shared" si="9"/>
+        <v>88</v>
+      </c>
+      <c r="AI140">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ140" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG4</v>
+      </c>
+      <c r="AK140" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -16881,8 +19517,27 @@
       <c r="AF141">
         <v>89</v>
       </c>
+      <c r="AG141">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH141" s="6">
+        <f t="shared" si="9"/>
+        <v>89</v>
+      </c>
+      <c r="AI141">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ141" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_north_P1</v>
+      </c>
+      <c r="AK141" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -16979,8 +19634,27 @@
       <c r="AF142">
         <v>89</v>
       </c>
+      <c r="AG142">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH142" s="6">
+        <f t="shared" si="9"/>
+        <v>89</v>
+      </c>
+      <c r="AI142">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ142" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_north_P1</v>
+      </c>
+      <c r="AK142" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -17077,8 +19751,27 @@
       <c r="AF143">
         <v>89</v>
       </c>
+      <c r="AG143">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH143" s="6">
+        <f t="shared" si="9"/>
+        <v>89</v>
+      </c>
+      <c r="AI143">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ143" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_north_P1</v>
+      </c>
+      <c r="AK143" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -17175,8 +19868,27 @@
       <c r="AF144">
         <v>89</v>
       </c>
+      <c r="AG144">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH144" s="6">
+        <f t="shared" si="9"/>
+        <v>89</v>
+      </c>
+      <c r="AI144">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ144" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_north_P1</v>
+      </c>
+      <c r="AK144" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -17273,8 +19985,27 @@
       <c r="AF145">
         <v>90</v>
       </c>
+      <c r="AG145">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH145" s="6">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+      <c r="AI145">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ145" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_P1</v>
+      </c>
+      <c r="AK145" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -17371,8 +20102,27 @@
       <c r="AF146">
         <v>90</v>
       </c>
+      <c r="AG146">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH146" s="6">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+      <c r="AI146">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ146" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_P1</v>
+      </c>
+      <c r="AK146" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -17469,8 +20219,27 @@
       <c r="AF147">
         <v>90</v>
       </c>
+      <c r="AG147">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH147" s="6">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+      <c r="AI147">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ147" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_P1</v>
+      </c>
+      <c r="AK147" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -17567,8 +20336,27 @@
       <c r="AF148">
         <v>90</v>
       </c>
+      <c r="AG148">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH148" s="6">
+        <f t="shared" si="9"/>
+        <v>90</v>
+      </c>
+      <c r="AI148">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ148" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_P1</v>
+      </c>
+      <c r="AK148" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -17665,8 +20453,27 @@
       <c r="AF149">
         <v>91</v>
       </c>
+      <c r="AG149">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH149" s="6">
+        <f t="shared" si="9"/>
+        <v>91</v>
+      </c>
+      <c r="AI149">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ149" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_south_P5</v>
+      </c>
+      <c r="AK149" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -17763,8 +20570,27 @@
       <c r="AF150">
         <v>91</v>
       </c>
+      <c r="AG150">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH150" s="6">
+        <f t="shared" si="9"/>
+        <v>91</v>
+      </c>
+      <c r="AI150">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ150" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_south_P5</v>
+      </c>
+      <c r="AK150" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -17861,8 +20687,27 @@
       <c r="AF151">
         <v>91</v>
       </c>
+      <c r="AG151">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH151" s="6">
+        <f t="shared" si="9"/>
+        <v>91</v>
+      </c>
+      <c r="AI151">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ151" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_south_P5</v>
+      </c>
+      <c r="AK151" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -17959,8 +20804,27 @@
       <c r="AF152">
         <v>91</v>
       </c>
+      <c r="AG152">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AH152" s="6">
+        <f t="shared" si="9"/>
+        <v>91</v>
+      </c>
+      <c r="AI152">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="AJ152" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_south_P5</v>
+      </c>
+      <c r="AK152" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="153" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -18057,8 +20921,30 @@
       <c r="AF153">
         <v>92</v>
       </c>
+      <c r="AG153">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH153" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI153">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="AJ153" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_south_2</v>
+      </c>
+      <c r="AK153" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL153" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="154" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -18155,8 +21041,30 @@
       <c r="AF154">
         <v>93</v>
       </c>
+      <c r="AG154">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH154" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI154">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="AJ154" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_south_2</v>
+      </c>
+      <c r="AK154" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL154" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="155" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -18253,8 +21161,30 @@
       <c r="AF155">
         <v>94</v>
       </c>
+      <c r="AG155">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH155" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI155">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="AJ155" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_south_2</v>
+      </c>
+      <c r="AK155" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL155" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="156" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -18351,8 +21281,30 @@
       <c r="AF156">
         <v>95</v>
       </c>
+      <c r="AG156">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH156" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI156">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="AJ156" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_south_2</v>
+      </c>
+      <c r="AK156" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL156" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="157" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -18449,8 +21401,27 @@
       <c r="AF157">
         <v>96</v>
       </c>
+      <c r="AG157">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH157" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI157">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ157" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG1</v>
+      </c>
+      <c r="AK157" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="158" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -18547,8 +21518,27 @@
       <c r="AF158">
         <v>96</v>
       </c>
+      <c r="AG158">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH158" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI158">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ158" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG1</v>
+      </c>
+      <c r="AK158" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="159" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -18645,8 +21635,27 @@
       <c r="AF159">
         <v>96</v>
       </c>
+      <c r="AG159">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH159" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI159">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ159" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C1</v>
+      </c>
+      <c r="AK159" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="160" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -18743,8 +21752,27 @@
       <c r="AF160">
         <v>96</v>
       </c>
+      <c r="AG160">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH160" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI160">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ160" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG2</v>
+      </c>
+      <c r="AK160" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="161" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -18841,8 +21869,27 @@
       <c r="AF161">
         <v>96</v>
       </c>
+      <c r="AG161">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH161" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI161">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ161" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C2</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="162" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -18939,8 +21986,27 @@
       <c r="AF162">
         <v>96</v>
       </c>
+      <c r="AG162">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH162" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI162">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ162" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG2</v>
+      </c>
+      <c r="AK162" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="163" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -19037,8 +22103,27 @@
       <c r="AF163">
         <v>96</v>
       </c>
+      <c r="AG163">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH163" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI163">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ163" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C3</v>
+      </c>
+      <c r="AK163" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="164" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -19135,8 +22220,27 @@
       <c r="AF164">
         <v>96</v>
       </c>
+      <c r="AG164">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH164" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI164">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ164" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG3</v>
+      </c>
+      <c r="AK164" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="165" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -19233,8 +22337,27 @@
       <c r="AF165">
         <v>96</v>
       </c>
+      <c r="AG165">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH165" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI165">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ165" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_C4</v>
+      </c>
+      <c r="AK165" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="166" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -19331,8 +22454,27 @@
       <c r="AF166">
         <v>96</v>
       </c>
+      <c r="AG166">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH166" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI166">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ166" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_BG4</v>
+      </c>
+      <c r="AK166" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="167" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -19429,8 +22571,27 @@
       <c r="AF167">
         <v>96</v>
       </c>
+      <c r="AG167">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH167" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI167">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ167" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG3</v>
+      </c>
+      <c r="AK167" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="168" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -19527,8 +22688,27 @@
       <c r="AF168">
         <v>96</v>
       </c>
+      <c r="AG168">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="AH168" s="6">
+        <f t="shared" si="9"/>
+        <v>96</v>
+      </c>
+      <c r="AI168">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ168" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_AG4</v>
+      </c>
+      <c r="AK168" t="s">
+        <v>711</v>
+      </c>
     </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -19625,8 +22805,27 @@
       <c r="AF169">
         <v>97</v>
       </c>
+      <c r="AG169">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH169" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI169">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="AJ169" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_south_2</v>
+      </c>
+      <c r="AL169" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -19723,8 +22922,24 @@
       <c r="AF170">
         <v>98</v>
       </c>
+      <c r="AG170">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH170" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI170">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ170" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -19821,8 +23036,27 @@
       <c r="AF171">
         <v>99</v>
       </c>
+      <c r="AG171">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH171" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI171">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ171" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_1</v>
+      </c>
+      <c r="AK171" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -19919,8 +23153,27 @@
       <c r="AF172">
         <v>100</v>
       </c>
+      <c r="AG172">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH172" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI172">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ172" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_1</v>
+      </c>
+      <c r="AK172" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -20017,8 +23270,30 @@
       <c r="AF173">
         <v>101</v>
       </c>
+      <c r="AG173">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH173" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI173">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ173" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_2</v>
+      </c>
+      <c r="AK173" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL173" t="s">
+        <v>716</v>
+      </c>
     </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -20115,8 +23390,30 @@
       <c r="AF174">
         <v>102</v>
       </c>
+      <c r="AG174">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH174" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI174">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ174" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_2</v>
+      </c>
+      <c r="AK174" t="s">
+        <v>409</v>
+      </c>
+      <c r="AL174" t="s">
+        <v>716</v>
+      </c>
     </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -20213,8 +23510,27 @@
       <c r="AF175">
         <v>103</v>
       </c>
+      <c r="AG175">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH175" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI175">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ175" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_3</v>
+      </c>
+      <c r="AK175" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -20311,8 +23627,27 @@
       <c r="AF176">
         <v>104</v>
       </c>
+      <c r="AG176">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH176" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI176">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ176" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>JSP_mid_3</v>
+      </c>
+      <c r="AK176" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -20409,8 +23744,24 @@
       <c r="AF177">
         <v>105</v>
       </c>
+      <c r="AG177">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH177" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI177">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ177" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -20507,8 +23858,24 @@
       <c r="AF178">
         <v>106</v>
       </c>
+      <c r="AG178">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH178" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI178">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ178" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -20605,8 +23972,24 @@
       <c r="AF179">
         <v>107</v>
       </c>
+      <c r="AG179">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH179" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI179">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ179" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -20703,8 +24086,24 @@
       <c r="AF180">
         <v>108</v>
       </c>
+      <c r="AG180">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH180" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI180">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ180" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -20801,8 +24200,24 @@
       <c r="AF181">
         <v>109</v>
       </c>
+      <c r="AG181">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH181" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI181">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ181" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -20899,8 +24314,24 @@
       <c r="AF182">
         <v>110</v>
       </c>
+      <c r="AG182">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH182" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI182">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ182" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -20997,8 +24428,24 @@
       <c r="AF183">
         <v>111</v>
       </c>
+      <c r="AG183">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH183" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI183">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ183" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -21095,8 +24542,24 @@
       <c r="AF184">
         <v>112</v>
       </c>
+      <c r="AG184">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH184" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI184">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ184" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -21193,8 +24656,24 @@
       <c r="AF185">
         <v>113</v>
       </c>
+      <c r="AG185">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH185" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI185">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ185" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -21291,8 +24770,24 @@
       <c r="AF186">
         <v>114</v>
       </c>
+      <c r="AG186">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AH186" s="6">
+        <f t="shared" si="9"/>
+        <v>114</v>
+      </c>
+      <c r="AI186">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ186" t="str">
+        <f t="shared" si="11"/>
+        <v>MCD_south_L1</v>
+      </c>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -21389,8 +24884,24 @@
       <c r="AF187">
         <v>114</v>
       </c>
+      <c r="AG187">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AH187" s="6">
+        <f t="shared" si="9"/>
+        <v>114</v>
+      </c>
+      <c r="AI187">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ187" t="str">
+        <f t="shared" si="11"/>
+        <v>MCD_south_L1</v>
+      </c>
     </row>
-    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -21487,8 +24998,24 @@
       <c r="AF188">
         <v>115</v>
       </c>
+      <c r="AG188">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AH188" s="6">
+        <f t="shared" si="9"/>
+        <v>115</v>
+      </c>
+      <c r="AI188">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ188" t="str">
+        <f t="shared" si="11"/>
+        <v>MCD_north_L1</v>
+      </c>
     </row>
-    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -21585,8 +25112,24 @@
       <c r="AF189">
         <v>115</v>
       </c>
+      <c r="AG189">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AH189" s="6">
+        <f t="shared" si="9"/>
+        <v>115</v>
+      </c>
+      <c r="AI189">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="AJ189" t="str">
+        <f t="shared" si="11"/>
+        <v>MCD_north_L1</v>
+      </c>
     </row>
-    <row r="190" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -21683,8 +25226,24 @@
       <c r="AF190">
         <v>116</v>
       </c>
+      <c r="AG190">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH190" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI190">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ190" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -21781,8 +25340,24 @@
       <c r="AF191">
         <v>117</v>
       </c>
+      <c r="AG191">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH191" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI191">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ191" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -21879,8 +25454,24 @@
       <c r="AF192">
         <v>118</v>
       </c>
+      <c r="AG192">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH192" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI192">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ192" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -21977,8 +25568,24 @@
       <c r="AF193">
         <v>119</v>
       </c>
+      <c r="AG193">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH193" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI193">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ193" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -22075,8 +25682,24 @@
       <c r="AF194">
         <v>120</v>
       </c>
+      <c r="AG194">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="AH194" s="6" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI194">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="AJ194" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
     </row>
-    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -22173,8 +25796,24 @@
       <c r="AF195">
         <v>121</v>
       </c>
+      <c r="AG195">
+        <f t="shared" ref="AG195:AG258" si="12">COUNTIF(AF:AF,AF195)</f>
+        <v>1</v>
+      </c>
+      <c r="AH195" s="6" t="str">
+        <f t="shared" ref="AH195:AH258" si="13">IF(AG195&gt;1,AF195,"")</f>
+        <v/>
+      </c>
+      <c r="AI195">
+        <f t="shared" ref="AI195:AI258" si="14">COUNTIF(D:D,D195)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ195" t="str">
+        <f t="shared" ref="AJ195:AJ258" si="15">IF(AI195&gt;1,D195,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -22271,8 +25910,27 @@
       <c r="AF196">
         <v>122</v>
       </c>
+      <c r="AG196">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH196" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI196">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ196" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_still_2</v>
+      </c>
+      <c r="AK196" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -22369,8 +26027,27 @@
       <c r="AF197">
         <v>123</v>
       </c>
+      <c r="AG197">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH197" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI197">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ197" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_still_2</v>
+      </c>
+      <c r="AK197" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -22467,8 +26144,24 @@
       <c r="AF198">
         <v>124</v>
       </c>
+      <c r="AG198">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH198" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI198">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ198" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -22565,8 +26258,24 @@
       <c r="AF199">
         <v>125</v>
       </c>
+      <c r="AG199">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH199" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI199">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ199" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -22663,8 +26372,24 @@
       <c r="AF200">
         <v>126</v>
       </c>
+      <c r="AG200">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AH200" s="6">
+        <f t="shared" si="13"/>
+        <v>126</v>
+      </c>
+      <c r="AI200">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ200" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_south_L2</v>
+      </c>
     </row>
-    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -22761,8 +26486,24 @@
       <c r="AF201">
         <v>126</v>
       </c>
+      <c r="AG201">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AH201" s="6">
+        <f t="shared" si="13"/>
+        <v>126</v>
+      </c>
+      <c r="AI201">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ201" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_south_L2</v>
+      </c>
     </row>
-    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -22859,8 +26600,24 @@
       <c r="AF202">
         <v>127</v>
       </c>
+      <c r="AG202">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AH202" s="6">
+        <f t="shared" si="13"/>
+        <v>127</v>
+      </c>
+      <c r="AI202">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ202" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_south_L1</v>
+      </c>
     </row>
-    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -22957,8 +26714,24 @@
       <c r="AF203">
         <v>127</v>
       </c>
+      <c r="AG203">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AH203" s="6">
+        <f t="shared" si="13"/>
+        <v>127</v>
+      </c>
+      <c r="AI203">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ203" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_south_L1</v>
+      </c>
     </row>
-    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -23055,8 +26828,24 @@
       <c r="AF204">
         <v>128</v>
       </c>
+      <c r="AG204">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AH204" s="6">
+        <f t="shared" si="13"/>
+        <v>128</v>
+      </c>
+      <c r="AI204">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ204" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_south_L3</v>
+      </c>
     </row>
-    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -23153,8 +26942,24 @@
       <c r="AF205">
         <v>128</v>
       </c>
+      <c r="AG205">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="AH205" s="6">
+        <f t="shared" si="13"/>
+        <v>128</v>
+      </c>
+      <c r="AI205">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ205" t="str">
+        <f t="shared" si="15"/>
+        <v>MCN_south_L3</v>
+      </c>
     </row>
-    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -23251,8 +27056,24 @@
       <c r="AF206">
         <v>129</v>
       </c>
+      <c r="AG206">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH206" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI206">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ206" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -23349,8 +27170,24 @@
       <c r="AF207">
         <v>130</v>
       </c>
+      <c r="AG207">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH207" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI207">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ207" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -23447,8 +27284,27 @@
       <c r="AF208">
         <v>131</v>
       </c>
+      <c r="AG208">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH208" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI208">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ208" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>MRE_1</v>
+      </c>
+      <c r="AK208" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -23545,8 +27401,27 @@
       <c r="AF209">
         <v>132</v>
       </c>
+      <c r="AG209">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH209" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI209">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ209" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>MRE_1</v>
+      </c>
+      <c r="AK209" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -23643,8 +27518,27 @@
       <c r="AF210">
         <v>133</v>
       </c>
+      <c r="AG210">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH210" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI210">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ210" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>MRE_2</v>
+      </c>
+      <c r="AK210" s="8" t="s">
+        <v>717</v>
+      </c>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -23741,8 +27635,27 @@
       <c r="AF211">
         <v>134</v>
       </c>
+      <c r="AG211">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH211" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI211">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ211" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>MRE_2</v>
+      </c>
+      <c r="AK211" s="8" t="s">
+        <v>717</v>
+      </c>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -23839,8 +27752,24 @@
       <c r="AF212">
         <v>135</v>
       </c>
+      <c r="AG212">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH212" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI212">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ212" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -23937,8 +27866,24 @@
       <c r="AF213">
         <v>136</v>
       </c>
+      <c r="AG213">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH213" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI213">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ213" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -24035,8 +27980,24 @@
       <c r="AF214">
         <v>137</v>
       </c>
+      <c r="AG214">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH214" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI214">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ214" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -24133,8 +28094,24 @@
       <c r="AF215">
         <v>138</v>
       </c>
+      <c r="AG215">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH215" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI215">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ215" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="216" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -24231,8 +28208,24 @@
       <c r="AF216">
         <v>139</v>
       </c>
+      <c r="AG216">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH216" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI216">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ216" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="217" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -24329,8 +28322,24 @@
       <c r="AF217">
         <v>140</v>
       </c>
+      <c r="AG217">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH217" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI217">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ217" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -24427,8 +28436,24 @@
       <c r="AF218">
         <v>141</v>
       </c>
+      <c r="AG218">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH218" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI218">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ218" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -24525,8 +28550,24 @@
       <c r="AF219">
         <v>142</v>
       </c>
+      <c r="AG219">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH219" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI219">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ219" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -24623,8 +28664,24 @@
       <c r="AF220">
         <v>143</v>
       </c>
+      <c r="AG220">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH220" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI220">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ220" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="221" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -24721,8 +28778,24 @@
       <c r="AF221">
         <v>144</v>
       </c>
+      <c r="AG221">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH221" s="6">
+        <f t="shared" si="13"/>
+        <v>144</v>
+      </c>
+      <c r="AI221">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ221" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P1</v>
+      </c>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -24819,8 +28892,24 @@
       <c r="AF222">
         <v>144</v>
       </c>
+      <c r="AG222">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH222" s="6">
+        <f t="shared" si="13"/>
+        <v>144</v>
+      </c>
+      <c r="AI222">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ222" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P1</v>
+      </c>
     </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -24917,8 +29006,24 @@
       <c r="AF223">
         <v>144</v>
       </c>
+      <c r="AG223">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH223" s="6">
+        <f t="shared" si="13"/>
+        <v>144</v>
+      </c>
+      <c r="AI223">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ223" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P1</v>
+      </c>
     </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -25015,8 +29120,24 @@
       <c r="AF224">
         <v>144</v>
       </c>
+      <c r="AG224">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH224" s="6">
+        <f t="shared" si="13"/>
+        <v>144</v>
+      </c>
+      <c r="AI224">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ224" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P1</v>
+      </c>
     </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -25113,8 +29234,24 @@
       <c r="AF225">
         <v>145</v>
       </c>
+      <c r="AG225">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH225" s="6">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="AI225">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ225" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P2</v>
+      </c>
     </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -25211,8 +29348,24 @@
       <c r="AF226">
         <v>145</v>
       </c>
+      <c r="AG226">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH226" s="6">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="AI226">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ226" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P2</v>
+      </c>
     </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -25309,8 +29462,24 @@
       <c r="AF227">
         <v>145</v>
       </c>
+      <c r="AG227">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH227" s="6">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="AI227">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ227" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P2</v>
+      </c>
     </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -25407,8 +29576,24 @@
       <c r="AF228">
         <v>145</v>
       </c>
+      <c r="AG228">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH228" s="6">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="AI228">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ228" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P2</v>
+      </c>
     </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -25505,8 +29690,24 @@
       <c r="AF229">
         <v>146</v>
       </c>
+      <c r="AG229">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH229" s="6">
+        <f t="shared" si="13"/>
+        <v>146</v>
+      </c>
+      <c r="AI229">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ229" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P3</v>
+      </c>
     </row>
-    <row r="230" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -25603,8 +29804,24 @@
       <c r="AF230">
         <v>146</v>
       </c>
+      <c r="AG230">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH230" s="6">
+        <f t="shared" si="13"/>
+        <v>146</v>
+      </c>
+      <c r="AI230">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ230" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P3</v>
+      </c>
     </row>
-    <row r="231" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -25701,8 +29918,24 @@
       <c r="AF231">
         <v>146</v>
       </c>
+      <c r="AG231">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH231" s="6">
+        <f t="shared" si="13"/>
+        <v>146</v>
+      </c>
+      <c r="AI231">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ231" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P3</v>
+      </c>
     </row>
-    <row r="232" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -25799,8 +30032,24 @@
       <c r="AF232">
         <v>146</v>
       </c>
+      <c r="AG232">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH232" s="6">
+        <f t="shared" si="13"/>
+        <v>146</v>
+      </c>
+      <c r="AI232">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ232" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P3</v>
+      </c>
     </row>
-    <row r="233" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -25897,8 +30146,24 @@
       <c r="AF233">
         <v>147</v>
       </c>
+      <c r="AG233">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH233" s="6">
+        <f t="shared" si="13"/>
+        <v>147</v>
+      </c>
+      <c r="AI233">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ233" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P4</v>
+      </c>
     </row>
-    <row r="234" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -25995,8 +30260,24 @@
       <c r="AF234">
         <v>147</v>
       </c>
+      <c r="AG234">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH234" s="6">
+        <f t="shared" si="13"/>
+        <v>147</v>
+      </c>
+      <c r="AI234">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ234" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P4</v>
+      </c>
     </row>
-    <row r="235" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -26093,8 +30374,24 @@
       <c r="AF235">
         <v>147</v>
       </c>
+      <c r="AG235">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH235" s="6">
+        <f t="shared" si="13"/>
+        <v>147</v>
+      </c>
+      <c r="AI235">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ235" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P4</v>
+      </c>
     </row>
-    <row r="236" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -26191,8 +30488,24 @@
       <c r="AF236">
         <v>147</v>
       </c>
+      <c r="AG236">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="AH236" s="6">
+        <f t="shared" si="13"/>
+        <v>147</v>
+      </c>
+      <c r="AI236">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="AJ236" t="str">
+        <f t="shared" si="15"/>
+        <v>PTG_P4</v>
+      </c>
     </row>
-    <row r="237" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -26289,8 +30602,24 @@
       <c r="AF237">
         <v>148</v>
       </c>
+      <c r="AG237">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH237" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI237">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ237" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="238" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -26387,8 +30716,24 @@
       <c r="AF238">
         <v>149</v>
       </c>
+      <c r="AG238">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH238" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI238">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ238" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="239" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -26485,8 +30830,27 @@
       <c r="AF239">
         <v>150</v>
       </c>
+      <c r="AG239">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH239" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI239">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AJ239" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_4S</v>
+      </c>
+      <c r="AK239" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="240" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -26583,8 +30947,24 @@
       <c r="AF240">
         <v>151</v>
       </c>
+      <c r="AG240">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH240" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI240">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ240" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="241" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -26681,8 +31061,24 @@
       <c r="AF241">
         <v>152</v>
       </c>
+      <c r="AG241">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH241" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI241">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ241" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="242" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -26779,8 +31175,24 @@
       <c r="AF242">
         <v>153</v>
       </c>
+      <c r="AG242">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH242" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI242">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ242" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="243" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -26877,8 +31289,24 @@
       <c r="AF243">
         <v>154</v>
       </c>
+      <c r="AG243">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH243" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI243">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ243" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="244" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -26975,8 +31403,24 @@
       <c r="AF244">
         <v>155</v>
       </c>
+      <c r="AG244">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH244" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI244">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ244" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="245" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -27073,8 +31517,24 @@
       <c r="AF245">
         <v>156</v>
       </c>
+      <c r="AG245">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH245" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI245">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ245" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="246" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -27171,8 +31631,27 @@
       <c r="AF246">
         <v>157</v>
       </c>
+      <c r="AG246">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH246" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI246">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AJ246" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_4S</v>
+      </c>
+      <c r="AK246" t="s">
+        <v>718</v>
+      </c>
     </row>
-    <row r="247" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -27269,8 +31748,27 @@
       <c r="AF247">
         <v>158</v>
       </c>
+      <c r="AG247">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH247" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI247">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AJ247" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_4S</v>
+      </c>
+      <c r="AK247" t="s">
+        <v>718</v>
+      </c>
     </row>
-    <row r="248" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -27367,8 +31865,27 @@
       <c r="AF248">
         <v>159</v>
       </c>
+      <c r="AG248">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH248" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI248">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AJ248" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_4S</v>
+      </c>
+      <c r="AK248" t="s">
+        <v>718</v>
+      </c>
     </row>
-    <row r="249" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -27465,8 +31982,27 @@
       <c r="AF249">
         <v>160</v>
       </c>
+      <c r="AG249">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH249" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI249">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ249" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_5a</v>
+      </c>
+      <c r="AK249" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="250" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -27563,8 +32099,27 @@
       <c r="AF250">
         <v>161</v>
       </c>
+      <c r="AG250">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH250" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI250">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="AJ250" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_5a</v>
+      </c>
+      <c r="AK250" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="251" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -27661,8 +32216,27 @@
       <c r="AF251">
         <v>162</v>
       </c>
+      <c r="AG251">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH251" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI251">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AJ251" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_4S</v>
+      </c>
+      <c r="AK251" t="s">
+        <v>718</v>
+      </c>
     </row>
-    <row r="252" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -27759,8 +32333,27 @@
       <c r="AF252">
         <v>163</v>
       </c>
+      <c r="AG252">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH252" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI252">
+        <f t="shared" si="14"/>
+        <v>6</v>
+      </c>
+      <c r="AJ252" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>QMH_4S</v>
+      </c>
+      <c r="AK252" t="s">
+        <v>718</v>
+      </c>
     </row>
-    <row r="253" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -27857,8 +32450,24 @@
       <c r="AF253">
         <v>164</v>
       </c>
+      <c r="AG253">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH253" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI253">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ253" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="254" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -27955,8 +32564,24 @@
       <c r="AF254">
         <v>165</v>
       </c>
+      <c r="AG254">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH254" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI254">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ254" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="255" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -28053,8 +32678,24 @@
       <c r="AF255">
         <v>166</v>
       </c>
+      <c r="AG255">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH255" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI255">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ255" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="256" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -28151,8 +32792,24 @@
       <c r="AF256">
         <v>167</v>
       </c>
+      <c r="AG256">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH256" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI256">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ256" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="257" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -28249,8 +32906,24 @@
       <c r="AF257">
         <v>168</v>
       </c>
+      <c r="AG257">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH257" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI257">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ257" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="258" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -28347,8 +33020,24 @@
       <c r="AF258">
         <v>169</v>
       </c>
+      <c r="AG258">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AH258" s="6" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AI258">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="AJ258" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
     </row>
-    <row r="259" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -28445,8 +33134,24 @@
       <c r="AF259">
         <v>170</v>
       </c>
+      <c r="AG259">
+        <f t="shared" ref="AG259:AG289" si="16">COUNTIF(AF:AF,AF259)</f>
+        <v>1</v>
+      </c>
+      <c r="AH259" s="6" t="str">
+        <f t="shared" ref="AH259:AH289" si="17">IF(AG259&gt;1,AF259,"")</f>
+        <v/>
+      </c>
+      <c r="AI259">
+        <f t="shared" ref="AI259:AI289" si="18">COUNTIF(D:D,D259)</f>
+        <v>1</v>
+      </c>
+      <c r="AJ259" t="str">
+        <f t="shared" ref="AJ259:AJ289" si="19">IF(AI259&gt;1,D259,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="260" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -28543,8 +33248,24 @@
       <c r="AF260">
         <v>171</v>
       </c>
+      <c r="AG260">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH260" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI260">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ260" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="261" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -28641,8 +33362,24 @@
       <c r="AF261">
         <v>172</v>
       </c>
+      <c r="AG261">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH261" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI261">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ261" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="262" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -28739,8 +33476,24 @@
       <c r="AF262">
         <v>173</v>
       </c>
+      <c r="AG262">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH262" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI262">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ262" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="263" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -28837,8 +33590,24 @@
       <c r="AF263">
         <v>174</v>
       </c>
+      <c r="AG263">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH263" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI263">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ263" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="264" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -28935,8 +33704,24 @@
       <c r="AF264">
         <v>175</v>
       </c>
+      <c r="AG264">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH264" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI264">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ264" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="265" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -29033,8 +33818,24 @@
       <c r="AF265">
         <v>176</v>
       </c>
+      <c r="AG265">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH265" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI265">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ265" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="266" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -29131,8 +33932,24 @@
       <c r="AF266">
         <v>177</v>
       </c>
+      <c r="AG266">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH266" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI266">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ266" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="267" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -29229,8 +34046,24 @@
       <c r="AF267">
         <v>178</v>
       </c>
+      <c r="AG267">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH267" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI267">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ267" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="268" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -29327,8 +34160,24 @@
       <c r="AF268">
         <v>179</v>
       </c>
+      <c r="AG268">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH268" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI268">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ268" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="269" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -29425,8 +34274,24 @@
       <c r="AF269">
         <v>180</v>
       </c>
+      <c r="AG269">
+        <f t="shared" si="16"/>
+        <v>2</v>
+      </c>
+      <c r="AH269" s="6">
+        <f t="shared" si="17"/>
+        <v>180</v>
+      </c>
+      <c r="AI269">
+        <f t="shared" si="18"/>
+        <v>2</v>
+      </c>
+      <c r="AJ269" t="str">
+        <f t="shared" si="19"/>
+        <v>TAY_L1</v>
+      </c>
     </row>
-    <row r="270" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -29523,8 +34388,24 @@
       <c r="AF270">
         <v>180</v>
       </c>
+      <c r="AG270">
+        <f t="shared" si="16"/>
+        <v>2</v>
+      </c>
+      <c r="AH270" s="6">
+        <f t="shared" si="17"/>
+        <v>180</v>
+      </c>
+      <c r="AI270">
+        <f t="shared" si="18"/>
+        <v>2</v>
+      </c>
+      <c r="AJ270" t="str">
+        <f t="shared" si="19"/>
+        <v>TAY_L1</v>
+      </c>
     </row>
-    <row r="271" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -29621,8 +34502,24 @@
       <c r="AF271">
         <v>181</v>
       </c>
+      <c r="AG271">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH271" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI271">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ271" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="272" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -29719,8 +34616,24 @@
       <c r="AF272">
         <v>182</v>
       </c>
+      <c r="AG272">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH272" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI272">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ272" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="273" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -29817,8 +34730,24 @@
       <c r="AF273">
         <v>183</v>
       </c>
+      <c r="AG273">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH273" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI273">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ273" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="274" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -29915,8 +34844,24 @@
       <c r="AF274">
         <v>184</v>
       </c>
+      <c r="AG274">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH274" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI274">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ274" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="275" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -30013,8 +34958,24 @@
       <c r="AF275">
         <v>185</v>
       </c>
+      <c r="AG275">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH275" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI275">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ275" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="276" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -30111,8 +35072,24 @@
       <c r="AF276">
         <v>186</v>
       </c>
+      <c r="AG276">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH276" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI276">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ276" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="277" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -30209,8 +35186,27 @@
       <c r="AF277">
         <v>187</v>
       </c>
+      <c r="AG277">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH277" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI277">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AJ277" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>WES_test_1</v>
+      </c>
+      <c r="AK277" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="278" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -30307,8 +35303,27 @@
       <c r="AF278">
         <v>188</v>
       </c>
+      <c r="AG278">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH278" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI278">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AJ278" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>WES_test_1</v>
+      </c>
+      <c r="AK278" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="279" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -30405,8 +35420,27 @@
       <c r="AF279">
         <v>189</v>
       </c>
+      <c r="AG279">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH279" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI279">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AJ279" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>WES_test_1</v>
+      </c>
+      <c r="AK279" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="280" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -30503,8 +35537,27 @@
       <c r="AF280">
         <v>190</v>
       </c>
+      <c r="AG280">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH280" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI280">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AJ280" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>WES_test_1</v>
+      </c>
+      <c r="AK280" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="281" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -30601,8 +35654,27 @@
       <c r="AF281">
         <v>191</v>
       </c>
+      <c r="AG281">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH281" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI281">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="AJ281" s="7" t="str">
+        <f t="shared" si="19"/>
+        <v>WES_test_1</v>
+      </c>
+      <c r="AK281" t="s">
+        <v>409</v>
+      </c>
     </row>
-    <row r="282" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -30699,8 +35771,24 @@
       <c r="AF282">
         <v>192</v>
       </c>
+      <c r="AG282">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH282" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI282">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ282" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="283" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -30797,8 +35885,24 @@
       <c r="AF283">
         <v>193</v>
       </c>
+      <c r="AG283">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="AH283" s="6">
+        <f t="shared" si="17"/>
+        <v>193</v>
+      </c>
+      <c r="AI283">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
+      <c r="AJ283" t="str">
+        <f t="shared" si="19"/>
+        <v>ZAN_P1</v>
+      </c>
     </row>
-    <row r="284" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -30895,8 +35999,24 @@
       <c r="AF284">
         <v>193</v>
       </c>
+      <c r="AG284">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="AH284" s="6">
+        <f t="shared" si="17"/>
+        <v>193</v>
+      </c>
+      <c r="AI284">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
+      <c r="AJ284" t="str">
+        <f t="shared" si="19"/>
+        <v>ZAN_P1</v>
+      </c>
     </row>
-    <row r="285" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -30993,8 +36113,24 @@
       <c r="AF285">
         <v>193</v>
       </c>
+      <c r="AG285">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="AH285" s="6">
+        <f t="shared" si="17"/>
+        <v>193</v>
+      </c>
+      <c r="AI285">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
+      <c r="AJ285" t="str">
+        <f t="shared" si="19"/>
+        <v>ZAN_P1</v>
+      </c>
     </row>
-    <row r="286" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -31091,8 +36227,24 @@
       <c r="AF286">
         <v>193</v>
       </c>
+      <c r="AG286">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="AH286" s="6">
+        <f t="shared" si="17"/>
+        <v>193</v>
+      </c>
+      <c r="AI286">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
+      <c r="AJ286" t="str">
+        <f t="shared" si="19"/>
+        <v>ZAN_P1</v>
+      </c>
     </row>
-    <row r="287" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -31189,8 +36341,24 @@
       <c r="AF287">
         <v>194</v>
       </c>
+      <c r="AG287">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH287" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI287">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ287" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="288" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -31287,8 +36455,24 @@
       <c r="AF288">
         <v>195</v>
       </c>
+      <c r="AG288">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH288" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI288">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ288" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
-    <row r="289" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -31384,6 +36568,22 @@
       </c>
       <c r="AF289">
         <v>196</v>
+      </c>
+      <c r="AG289">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="AH289" s="6" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AI289">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="AJ289" t="str">
+        <f t="shared" si="19"/>
+        <v/>
       </c>
     </row>
   </sheetData>
